--- a/example_data/Model_Metadata.xlsx
+++ b/example_data/Model_Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be8e4b2583ae63f5/Área de Trabalho/Pós-doc/Aplicativo GC-MS metabolômica/my_first_streamlit_app/example_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{EED37E54-0242-4E86-9346-57F431E50ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC0B632F-3BC0-48F2-A5D4-B4C1AA1CB2AC}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{EED37E54-0242-4E86-9346-57F431E50ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50BAAFFA-A577-4D6F-91BD-8FFC298684AE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{03A8330D-7119-4605-938A-E59BC3BCBA89}"/>
   </bookViews>
@@ -59,132 +59,6 @@
     <t>ATTRIBUTE_family</t>
   </si>
   <si>
-    <t>CP-5P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LA-1P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LA-2P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LA-3P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LA-4P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LA-5P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LC-1P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LC-2P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LC-3P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LC-4P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LC-5P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LG-1P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LG-2P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LG-3P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LG-4P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LG-5P-SPLIT25-18625.CDF</t>
-  </si>
-  <si>
-    <t>LM-1P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>LM-2P-SPLIT25-18625.CDF</t>
-  </si>
-  <si>
-    <t>LM-3P-SPLIT25-18625.CDF</t>
-  </si>
-  <si>
-    <t>LM-4P-SPLIT25-18625.CDF</t>
-  </si>
-  <si>
-    <t>LM-5P-SPLIT25-18625.CDF</t>
-  </si>
-  <si>
-    <t>BRANCO-1P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>BRANCO-2P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CA-1P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CA-2P-SPLIT25-160625.CDF</t>
-  </si>
-  <si>
-    <t>CA-3P-SPLIT25-160625.CDF</t>
-  </si>
-  <si>
-    <t>CA-4P-SPLIT25-160625.CDF</t>
-  </si>
-  <si>
-    <t>CA-5P-SPLIT25-160625.CDF</t>
-  </si>
-  <si>
-    <t>CF-1P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CF-2P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CF-3P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CF-4P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CF-5P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CL-1P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CL-2P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CL-3P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CL-4P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CL-5P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CP-1P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CP-2P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CP-3P-SPLIT25.CDF</t>
-  </si>
-  <si>
-    <t>CP-4P-SPLIT25.CDF</t>
-  </si>
-  <si>
     <t>CA</t>
   </si>
   <si>
@@ -219,6 +93,132 @@
   </si>
   <si>
     <t>Sample</t>
+  </si>
+  <si>
+    <t>BRANCO-1P-SPLIT25</t>
+  </si>
+  <si>
+    <t>BRANCO-2P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CA-1P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CA-2P-SPLIT25-160625</t>
+  </si>
+  <si>
+    <t>CA-3P-SPLIT25-160625</t>
+  </si>
+  <si>
+    <t>CA-4P-SPLIT25-160625</t>
+  </si>
+  <si>
+    <t>CA-5P-SPLIT25-160625</t>
+  </si>
+  <si>
+    <t>CL-1P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CL-2P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CL-3P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CL-4P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CL-5P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CP-1P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CP-2P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CP-3P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CP-4P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CP-5P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CF-1P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CF-2P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CF-3P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CF-4P-SPLIT25</t>
+  </si>
+  <si>
+    <t>CF-5P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LA-1P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LA-2P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LA-3P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LA-4P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LA-5P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LC-1P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LC-2P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LC-3P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LC-4P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LC-5P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LG-1P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LG-2P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LG-3P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LG-4P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LG-5P-SPLIT25-18625</t>
+  </si>
+  <si>
+    <t>LM-1P-SPLIT25</t>
+  </si>
+  <si>
+    <t>LM-2P-SPLIT25-18625</t>
+  </si>
+  <si>
+    <t>LM-3P-SPLIT25-18625</t>
+  </si>
+  <si>
+    <t>LM-4P-SPLIT25-18625</t>
+  </si>
+  <si>
+    <t>LM-5P-SPLIT25-18625</t>
   </si>
 </sst>
 </file>
@@ -608,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -639,7 +639,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -656,682 +656,682 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
         <v>10</v>
       </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
-      </c>
       <c r="D26" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
